--- a/docs/original/04_ERD_테이블정의서.xlsx
+++ b/docs/original/04_ERD_테이블정의서.xlsx
@@ -2162,7 +2162,7 @@
     <row r="61" ht="16.5" customHeight="1" s="25">
       <c r="A61" s="14" t="inlineStr">
         <is>
-          <t xml:space="preserve">     created_at 은 21개 중 5개에만 있고, updated_at 은 어느 테이블에도 없다.</t>
+          <t xml:space="preserve">     created_at 은 21개 중 6개에만 있고, updated_at 은 어느 테이블에도 없다.</t>
         </is>
       </c>
     </row>
@@ -3843,7 +3843,7 @@
       </c>
       <c r="D24" s="29" t="inlineStr">
         <is>
-          <t>사장이 등록하는 직원별 근무 예정. 같은 직원의 같은 날짜에는 1건만 둔다.</t>
+          <t>사장이 등록하는 직원별 근무 예정. 같은 직원·같은 날짜의 중복을 DB에서 막지 않는다(유니크 제약 없음).</t>
         </is>
       </c>
       <c r="E24" s="28" t="inlineStr">
@@ -11375,7 +11375,7 @@
       </c>
       <c r="B201" s="29" t="inlineStr">
         <is>
-          <t>사장이 등록하는 직원별 근무 예정. 같은 직원의 같은 날짜에는 1건만 둔다.</t>
+          <t>사장이 등록하는 직원별 근무 예정. 같은 직원·같은 날짜의 중복을 DB에서 막지 않는다(유니크 제약 없음).</t>
         </is>
       </c>
       <c r="C201" s="31" t="n"/>
@@ -11597,7 +11597,7 @@
       <c r="J206" s="28" t="n"/>
       <c r="K206" s="29" t="inlineStr">
         <is>
-          <t>같은 직원의 같은 날짜에는 1건만 둔다</t>
+          <t>같은 직원·같은 날짜의 중복을 DB에서 막지 않는다(유니크 제약 없음)</t>
         </is>
       </c>
     </row>
